--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
@@ -6339,7 +6339,7 @@
         <v>69</v>
       </c>
       <c r="K8" s="129">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="N8" s="69" t="s">
         <v>189</v>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">通知メッセージ（既存リスト）：登録済みのスタッフに配信して友だち追加。リストは仮に3,000人、毎月リスト×15%×15%が友だちに（FMTの式）</t>
+          <t xml:space="preserve">通知メッセージ（既存リスト）：登録済みのスタッフに配信して友だち追加。リストは仮に5,000人（マイナビの求人10件×1件30人×4週ごと＝年約3,900人の新規登録＋それ以前から続けている方）。毎月リスト×15%×15%が友だちに（FMTの式）</t>
         </is>
       </c>
       <c r="O21" s="25" t="s">

--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
@@ -3095,15 +3095,17 @@
         <v>164</v>
       </c>
       <c r="H10" s="125">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>154</v>
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
-      <c r="N10" s="132" t="s">
-        <v>180</v>
+      <c r="N10" s="132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイトからの応募は、仮に月150件（新規登録は月約300人＝マイナビの求人10件×1件30人×4週ごと。そのうち自社サイトからの応募を半分と置いた。マイナビ経由はマイナビの完了画面で終わるので、サンクスLINE誘導の母数に入れない）</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
@@ -6395,15 +6397,17 @@
         <v>164</v>
       </c>
       <c r="H10" s="125">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="I10" s="22" t="s">
         <v>154</v>
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
-      <c r="N10" s="132" t="s">
-        <v>180</v>
+      <c r="N10" s="132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">サイトからの応募は、仮に月150件（新規登録は月約300人＝マイナビの求人10件×1件30人×4週ごと。そのうち自社サイトからの応募を半分と置いた。マイナビ経由はマイナビの完了画面で終わるので、サンクスLINE誘導の母数に入れない）</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">

--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72ED57BE-AF90-4E88-B733-C7F944D72E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27509D86-E120-406C-A84B-FE7DD42E9BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
+    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
     <sheet name="SIM①_コンサル" sheetId="1" r:id="rId1"/>
     <sheet name="SIM①_比較" sheetId="2" r:id="rId2"/>
-    <sheet name="SIM②_成果報酬" sheetId="3" r:id="rId100"/>
-    <sheet name="SIM②_比較" sheetId="4" r:id="rId101"/>
-    <sheet name="SIM考え方" sheetId="5" r:id="rId3"/>
+    <sheet name="SIM②_成果報酬" sheetId="3" r:id="rId3"/>
+    <sheet name="SIM②_比較" sheetId="4" r:id="rId4"/>
+    <sheet name="SIM考え方" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="198">
   <si>
     <t>項目</t>
     <rPh sb="0" eb="2">
@@ -1558,9 +1558,6 @@
     <t>CV③_再応募</t>
   </si>
   <si>
-    <t>株式会社横浜シミズ御中_LINEOA施策提案【SIM】（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
-  </si>
-  <si>
     <t>CV①新規応募：サイトのLINEボタン・離脱防止で友だちになった方（応募前）が、配信から応募した数。サンクスLINE誘導で友だちになった方は応募済みなので、新規応募には数えない</t>
   </si>
   <si>
@@ -1577,6 +1574,20 @@
   </si>
   <si>
     <t>離脱防止ポップアップ：初期1.5万円・月3万円</t>
+  </si>
+  <si>
+    <t>株式会社横浜シミズ御中_LINEOA施策提案【SIM】コンサル（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
+  </si>
+  <si>
+    <t>株式会社横浜シミズ御中_LINEOA施策提案【SIM】成果報酬（応募1件 8,000円）（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導＋通知メッセージ）</t>
+  </si>
+  <si>
+    <t>通知メッセージ（既存リスト）：登録済みのスタッフに配信して友だち追加。リストは仮に5,000人（マイナビの求人10件×1件30人×4週ごと＝年約3,900人の新規登録＋それ以前から続けている方）。毎月リスト×15%×15%が友だちに（FMTの式）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サンクスLINE誘導＝応募×遷移80%×追加40%（資料と同じ・定義テキストの係数）</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -2503,67 +2514,67 @@
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2949,10 +2960,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】コンサル（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導）</t>
-        </is>
+      <c r="A4" s="56" t="s">
+        <v>194</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3016,7 +3025,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="147" t="s">
+      <c r="A8" s="137" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -3039,17 +3048,17 @@
         <v>69</v>
       </c>
       <c r="K8" s="129">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="N8" s="69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="148"/>
+      <c r="A9" s="138"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
@@ -3079,7 +3088,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="147" t="s">
+      <c r="A10" s="137" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -3102,14 +3111,12 @@
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
-      <c r="N10" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトからの応募は、仮に月150件（新規登録は月約300人＝マイナビの求人10件×1件30人×4週ごと。そのうち自社サイトからの応募を半分と置いた。マイナビ経由はマイナビの完了画面で終わるので、サンクスLINE誘導の母数に入れない）</t>
-        </is>
+      <c r="N10" s="132" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="148"/>
+      <c r="A11" s="138"/>
       <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
@@ -3143,10 +3150,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="149" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="149"/>
+      <c r="A13" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="139"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
@@ -3189,7 +3196,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="150" t="s">
+      <c r="A14" s="140" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -3198,24 +3205,31 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>8947</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>8947</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>8947</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
@@ -3224,31 +3238,38 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="151"/>
+      <c r="A15" s="141"/>
       <c r="B15" s="20" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -3266,31 +3287,38 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="152"/>
+      <c r="A16" s="142"/>
       <c r="B16" s="20" t="s">
         <v>151</v>
       </c>
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>150</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -3308,7 +3336,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="150" t="s">
+      <c r="A17" s="140" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3353,7 +3381,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="151"/>
+      <c r="A18" s="141"/>
       <c r="B18" s="8" t="s">
         <v>172</v>
       </c>
@@ -3417,7 +3445,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="151"/>
+      <c r="A19" s="141"/>
       <c r="B19" s="8" t="s">
         <v>114</v>
       </c>
@@ -3471,13 +3499,14 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="151"/>
+      <c r="A20" s="141"/>
       <c r="B20" s="8" t="s">
         <v>112</v>
       </c>
@@ -3512,7 +3541,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="152"/>
+      <c r="A21" s="142"/>
       <c r="B21" s="8" t="s">
         <v>113</v>
       </c>
@@ -3555,7 +3584,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="153" t="s">
+      <c r="A22" s="143" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3601,7 +3630,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="151"/>
+      <c r="A23" s="141"/>
       <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
@@ -3611,21 +3640,27 @@
       </c>
       <c r="E23" s="46">
         <f t="shared" ref="E23:J23" si="3">IF(E18=FALSE,0,E14*$P$18*0.125*0.125)</f>
+        <v>90.867968750000003</v>
       </c>
       <c r="F23" s="46">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -3648,7 +3683,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="151"/>
+      <c r="A24" s="141"/>
       <c r="B24" s="6" t="s">
         <v>114</v>
       </c>
@@ -3658,21 +3693,27 @@
       </c>
       <c r="E24" s="46">
         <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,E16*0.8*0.4)</f>
+        <v>48</v>
       </c>
       <c r="F24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
@@ -3695,7 +3736,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="152"/>
+      <c r="A25" s="142"/>
       <c r="B25" s="6" t="s">
         <v>67</v>
       </c>
@@ -3705,21 +3746,27 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -3737,36 +3784,42 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="137" t="s">
+      <c r="A26" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="138"/>
+      <c r="B26" s="145"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>183.60296875</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>183.60296875</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>183.60296875</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
+        <v>183.60296875</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
+        <v>183.60296875</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
+        <v>183.60296875</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
       <c r="N26" s="72" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>40</v>
@@ -3781,10 +3834,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="137" t="s">
+      <c r="A27" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="138"/>
+      <c r="B27" s="145"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0</v>
@@ -3794,18 +3847,23 @@
       </c>
       <c r="F27" s="47">
         <f>+E$27*1.025</f>
+        <v>0.32799999999999996</v>
       </c>
       <c r="G27" s="47">
         <f>+F$27*1.025</f>
+        <v>0.33619999999999994</v>
       </c>
       <c r="H27" s="47">
         <f>+G$27*1.025</f>
+        <v>0.34460499999999994</v>
       </c>
       <c r="I27" s="47">
         <f>+H$27*1.025</f>
+        <v>0.35322012499999988</v>
       </c>
       <c r="J27" s="47">
         <f>+I$27*1.025</f>
+        <v>0.36205062812499983</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
@@ -3828,31 +3886,37 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="154" t="s">
+      <c r="A28" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="155"/>
+      <c r="B28" s="147"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>0</v>
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>183.60296875</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
+        <v>367.2059375</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="7"/>
+        <v>550.80890625000006</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="7"/>
+        <v>734.41187500000001</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="7"/>
+        <v>918.01484374999995</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="7"/>
+        <v>1101.6178124999999</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -3872,31 +3936,38 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="143" t="s">
+      <c r="A29" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="144"/>
+      <c r="B29" s="149"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>124.85001874999999</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
+        <v>246.76239000000001</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="8"/>
+        <v>365.62695196875006</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="8"/>
+        <v>481.32987081562504</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="8"/>
+        <v>593.75352588876956</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="8"/>
+        <v>702.77639153068674</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -3910,10 +3981,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="141" t="s">
+      <c r="A30" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="142"/>
+      <c r="B30" s="136"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -3952,31 +4023,38 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="137" t="s">
+      <c r="A31" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="138"/>
+      <c r="B31" s="145"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>0</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>45.62511094798802</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>90.176689873670455</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>133.61447932621081</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>140.71750395179583</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>173.5847267988284</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>205.45772379526699</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -3987,10 +4065,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="141" t="s">
+      <c r="A32" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="142"/>
+      <c r="B32" s="136"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -4016,7 +4094,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
       <c r="N32" s="69" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>125</v>
@@ -4026,6 +4104,7 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -4033,31 +4112,37 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="137" t="s">
+      <c r="A33" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="138"/>
+      <c r="B33" s="145"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="63">
         <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>12.722386706650502</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" ref="F33:G33" si="9">+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>25.145423137850411</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="9"/>
+        <v>37.257883658270323</v>
       </c>
       <c r="H33" s="63">
         <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>39.238534755789225</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" ref="I33:J33" si="10">+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>48.403433434288686</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="10"/>
+        <v>57.291096058295594</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -4069,34 +4154,42 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="11">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="143" t="s">
+      <c r="A34" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="144"/>
+      <c r="B34" s="149"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>0</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E29*E32*$P$28</f>
+        <v>499.40007500000002</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F29*F32*$P$28</f>
+        <v>987.04956000000016</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G29*G32*$P$28</f>
+        <v>1462.5078078750003</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
+        <v>1540.2555866100001</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
+        <v>1900.0112828440626</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
+        <v>2248.8844528981977</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -4108,34 +4201,42 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="143" t="s">
+      <c r="A35" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="144"/>
+      <c r="B35" s="149"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>0</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>119.61237019200897</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="12">+F31+F33+1.05*(F31+F33)</f>
+        <v>236.4103316736178</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="12"/>
+        <v>350.28834411818633</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="12"/>
+        <v>368.90987935054943</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="12"/>
+        <v>455.07572847789004</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="12"/>
+        <v>538.63508069980321</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -4147,14 +4248,16 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="145" t="s">
+      <c r="A36" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>新規応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
@@ -4164,39 +4267,42 @@
         <v>2</v>
       </c>
       <c r="F36" s="111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="111">
         <v>4</v>
       </c>
       <c r="H36" s="111">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36" s="111">
         <v>5</v>
       </c>
       <c r="J36" s="111">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>25</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>126</v>
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="146"/>
-      <c r="B37" s="6">
+      <c r="A37" s="151"/>
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -4222,6 +4328,7 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -4229,11 +4336,12 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="145" t="s">
+      <c r="A38" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>再応募</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -4243,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="111">
         <v>1</v>
@@ -4252,26 +4360,28 @@
         <v>2</v>
       </c>
       <c r="I38" s="111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" s="111">
         <v>3</v>
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>9</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O38" s="21" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="146"/>
-      <c r="B39" s="6">
+      <c r="A39" s="151"/>
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -4297,6 +4407,7 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -4307,34 +4418,42 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="139" t="s">
+      <c r="A40" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="140"/>
+      <c r="B40" s="153"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="13"/>
+        <v>2</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="13"/>
+        <v>4</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="13"/>
+        <v>5</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="13"/>
+        <v>6</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="13"/>
+        <v>7</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="13"/>
+        <v>10</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>34</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4345,24 +4464,31 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="14">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
+        <v>1.6720678611998739E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="15">+IFERROR(F40/F35,0)</f>
+        <v>1.6919734309760626E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="15"/>
+        <v>1.4273954825950513E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="15"/>
+        <v>1.6264134781542722E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="15"/>
+        <v>1.5382055253557863E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="15"/>
+        <v>1.85654450634887E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>116</v>
@@ -4378,7 +4504,7 @@
       <c r="I42" s="116"/>
       <c r="J42" s="116"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="29" t="s">
         <v>50</v>
       </c>
@@ -4389,251 +4515,303 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A44" s="137" t="s">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="138"/>
+      <c r="B44" s="145"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="16">+F75*F76</f>
+        <v>0</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A45" s="137" t="s">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="138"/>
+      <c r="B45" s="145"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E68)+SUM(E71:E72)</f>
+        <v>65000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" ref="F45:J45" si="17">SUM(F65:F68)+SUM(F71:F72)</f>
+        <v>65000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A46" s="137" t="s">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="138"/>
+      <c r="B46" s="145"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="18">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>326.79210150298837</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="18"/>
+        <v>326.79210150298837</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="18"/>
+        <v>326.79210150298826</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="18"/>
+        <v>326.79210150298843</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="18"/>
+        <v>326.79210150298843</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="18"/>
+        <v>326.79210150298843</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A47" s="137" t="s">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="138"/>
+      <c r="B47" s="145"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="19">+E51/E35</f>
+        <v>543.4220548899591</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="19"/>
+        <v>274.94568253361012</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="19"/>
+        <v>185.56141273735668</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="19"/>
+        <v>176.19479346671281</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="19"/>
+        <v>142.83337021160872</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>120.67539291267656</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A48" s="137" t="s">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="138"/>
+      <c r="B48" s="145"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="20">+SUM(E36:E39)/E35</f>
+        <v>1.6720678611998739E-2</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="20"/>
+        <v>1.6919734309760626E-2</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="20"/>
+        <v>1.4273954825950513E-2</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="20"/>
+        <v>1.6264134781542722E-2</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="20"/>
+        <v>1.5382055253557863E-2</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="20"/>
+        <v>1.85654450634887E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A49" s="139" t="s">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="140"/>
+      <c r="B49" s="153"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
+        <v>32500</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
+        <v>16250</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="21"/>
+        <v>13000</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="21"/>
+        <v>10833.333333333334</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="21"/>
+        <v>9285.7142857142862</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="21"/>
+        <v>6500</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A50" s="139" t="s">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="140"/>
+      <c r="B50" s="153"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>21</v>
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="22">+F36*$D$8+F38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004" hidden="1">
-      <c r="A51" s="135" t="s">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="136"/>
+      <c r="B51" s="155"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>295000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>65000</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="23">SUM(F45,F50)+F44</f>
+        <v>65000</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="23"/>
+        <v>65000</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="23"/>
+        <v>65000</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="23"/>
+        <v>65000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>65000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -4651,188 +4829,226 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="137" t="s">
+      <c r="A54" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="138"/>
+      <c r="B54" s="145"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>0</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="24">+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="137" t="s">
+      <c r="A55" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="138"/>
+      <c r="B55" s="145"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>215000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="25">SUM(F65:F72)+F54</f>
+        <v>215000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="137" t="s">
+      <c r="A56" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="138"/>
+      <c r="B56" s="145"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" ref="E56:J56" si="26">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>326.79210150298837</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="26"/>
+        <v>326.79210150298837</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="26"/>
+        <v>326.79210150298826</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="26"/>
+        <v>326.79210150298843</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="26"/>
+        <v>326.79210150298843</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="26"/>
+        <v>326.79210150298843</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="137" t="s">
+      <c r="A57" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="138"/>
+      <c r="B57" s="145"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>1797.4729507898646</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="27">+F61/F35</f>
+        <v>909.43571914963354</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="27"/>
+        <v>613.78005751587204</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="27"/>
+        <v>582.7981630052808</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="27"/>
+        <v>472.44883993070579</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="27"/>
+        <v>399.15706886500709</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="137" t="s">
+      <c r="A58" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="138"/>
+      <c r="B58" s="145"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="28">+SUM(E36:E39)/E35</f>
+        <v>1.6720678611998739E-2</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="28"/>
+        <v>1.6919734309760626E-2</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="28"/>
+        <v>1.4273954825950513E-2</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="28"/>
+        <v>1.6264134781542722E-2</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="28"/>
+        <v>1.5382055253557863E-2</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="28"/>
+        <v>1.85654450634887E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="139" t="s">
+      <c r="A59" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="140"/>
+      <c r="B59" s="153"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
+        <v>107500</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
+        <v>53750</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="29"/>
+        <v>43000</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="29"/>
+        <v>35833.333333333336</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="29"/>
+        <v>30714.285714285714</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="29"/>
+        <v>21500</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="139" t="s">
+      <c r="A60" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="140"/>
+      <c r="B60" s="153"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -4845,31 +5061,38 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="135" t="s">
+      <c r="A61" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="136"/>
+      <c r="B61" s="155"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>295000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>215000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="30">+SUM(F65:F72)+F54</f>
+        <v>215000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -4947,7 +5170,7 @@
         <v>30000</v>
       </c>
       <c r="N66" s="69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -4995,21 +5218,27 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="31">IF(E34&lt;5000,5000,15000)</f>
+        <v>5000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="N68" s="69" t="s">
         <v>176</v>
@@ -5163,24 +5392,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="32">SUM(E65:E72)+E54</f>
+        <v>215000</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5201,24 +5437,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="33">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>0</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -5227,39 +5470,47 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="34">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
@@ -5272,18 +5523,17 @@
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5329,19 +5579,22 @@
       </c>
       <c r="F3" s="84"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="85" t="s">
         <v>139</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
-        <f>+'SIM①_コンサル'!D24</f>
+      <c r="C4" s="86" t="str">
+        <f>+SIM①_コンサル!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
-        <f>+'SIM①_コンサル'!G51</f>
+        <f>+SIM①_コンサル!G51</f>
+        <v>65000</v>
       </c>
       <c r="E4" s="28">
-        <f>+'SIM①_コンサル'!J51</f>
+        <f>+SIM①_コンサル!J51</f>
+        <v>65000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5350,14 +5603,17 @@
         <v>140</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
-        <f>+'SIM①_コンサル'!D25</f>
+      <c r="C5" s="86" t="str">
+        <f>+SIM①_コンサル!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
-        <f>+'SIM①_コンサル'!G61</f>
+        <f>+SIM①_コンサル!G61</f>
+        <v>215000</v>
       </c>
       <c r="E5" s="28">
-        <f>+'SIM①_コンサル'!J61</f>
+        <f>+SIM①_コンサル!J61</f>
+        <v>215000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5367,13 +5623,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'SIM①_コンサル'!D28</f>
+        <f>+SIM①_コンサル!D28</f>
+        <v>0</v>
       </c>
       <c r="D6" s="87">
-        <f>+'SIM①_コンサル'!G28</f>
+        <f>+SIM①_コンサル!G28</f>
+        <v>550.80890625000006</v>
       </c>
       <c r="E6" s="87">
-        <f>+'SIM①_コンサル'!J28</f>
+        <f>+SIM①_コンサル!J28</f>
+        <v>1101.6178124999999</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5383,13 +5642,16 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'SIM①_コンサル'!D27</f>
+        <f>+SIM①_コンサル!D27</f>
+        <v>0</v>
       </c>
       <c r="D7" s="89">
-        <f>+'SIM①_コンサル'!G27</f>
+        <f>+SIM①_コンサル!G27</f>
+        <v>0.33619999999999994</v>
       </c>
       <c r="E7" s="89">
-        <f>+'SIM①_コンサル'!J27</f>
+        <f>+SIM①_コンサル!J27</f>
+        <v>0.36205062812499983</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5399,13 +5661,16 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'SIM①_コンサル'!D29</f>
+        <f>+SIM①_コンサル!D29</f>
+        <v>0</v>
       </c>
       <c r="D8" s="10">
-        <f>+'SIM①_コンサル'!G29</f>
+        <f>+SIM①_コンサル!G29</f>
+        <v>365.62695196875006</v>
       </c>
       <c r="E8" s="10">
-        <f>+'SIM①_コンサル'!J29</f>
+        <f>+SIM①_コンサル!J29</f>
+        <v>702.77639153068674</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5423,13 +5688,16 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'SIM①_コンサル'!D34</f>
+        <f>+SIM①_コンサル!D34</f>
+        <v>0</v>
       </c>
       <c r="D10" s="10">
-        <f>+'SIM①_コンサル'!G34</f>
+        <f>+SIM①_コンサル!G34</f>
+        <v>1462.5078078750003</v>
       </c>
       <c r="E10" s="10">
-        <f>+'SIM①_コンサル'!J34</f>
+        <f>+SIM①_コンサル!J34</f>
+        <v>2248.8844528981977</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5439,29 +5707,35 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'SIM①_コンサル'!D35</f>
+        <f>+SIM①_コンサル!D35</f>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
-        <f>+'SIM①_コンサル'!G35</f>
+        <f>+SIM①_コンサル!G35</f>
+        <v>350.28834411818633</v>
       </c>
       <c r="E11" s="10">
-        <f>+'SIM①_コンサル'!J35</f>
+        <f>+SIM①_コンサル!J35</f>
+        <v>538.63508069980321</v>
       </c>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="85" t="s">
         <v>146</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>185.56141273735668</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>120.67539291267656</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -5472,12 +5746,15 @@
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>613.78005751587204</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>399.15706886500709</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -5498,13 +5775,16 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'SIM①_コンサル'!$H$10</f>
+        <f>+SIM①_コンサル!$H$10</f>
+        <v>150</v>
       </c>
       <c r="D15" s="87">
-        <f>+'SIM①_コンサル'!$H$10</f>
+        <f>+SIM①_コンサル!$H$10</f>
+        <v>150</v>
       </c>
       <c r="E15" s="87">
-        <f>+'SIM①_コンサル'!$H$10</f>
+        <f>+SIM①_コンサル!$H$10</f>
+        <v>150</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5518,12 +5798,15 @@
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>SUM(C17:C20)</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
+        <v>5</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
+        <v>10</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5542,13 +5825,16 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'SIM①_コンサル'!D36</f>
+        <f>+SIM①_コンサル!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
-        <f>+'SIM①_コンサル'!G36</f>
+        <f>+SIM①_コンサル!G36</f>
+        <v>4</v>
       </c>
       <c r="E17" s="87">
-        <f>+'SIM①_コンサル'!J36</f>
+        <f>+SIM①_コンサル!J36</f>
+        <v>7</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5579,13 +5865,16 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'SIM①_コンサル'!D37</f>
+        <f>+SIM①_コンサル!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
-        <f>+'SIM①_コンサル'!G37</f>
+        <f>+SIM①_コンサル!G37</f>
+        <v>0</v>
       </c>
       <c r="E18" s="87">
-        <f>+'SIM①_コンサル'!J37</f>
+        <f>+SIM①_コンサル!J37</f>
+        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5605,6 +5894,7 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -5616,13 +5906,16 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'SIM①_コンサル'!D38</f>
+        <f>+SIM①_コンサル!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
-        <f>+'SIM①_コンサル'!G38</f>
+        <f>+SIM①_コンサル!G38</f>
+        <v>1</v>
       </c>
       <c r="E19" s="87">
-        <f>+'SIM①_コンサル'!J38</f>
+        <f>+SIM①_コンサル!J38</f>
+        <v>3</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5637,13 +5930,16 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'SIM①_コンサル'!D39</f>
+        <f>+SIM①_コンサル!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
-        <f>+'SIM①_コンサル'!G39</f>
+        <f>+SIM①_コンサル!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
-        <f>+'SIM①_コンサル'!J39</f>
+        <f>+SIM①_コンサル!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -5665,19 +5961,22 @@
       <c r="X21" s="34"/>
       <c r="Y21" s="35"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="85" t="s">
         <v>141</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>13000</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>6500</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5691,14 +5990,17 @@
         <v>142</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>43000</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>21500</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -5726,13 +6028,16 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'SIM①_コンサル'!E68+C29*C30</f>
+        <f>+SIM①_コンサル!E68+C29*C30</f>
+        <v>5000</v>
       </c>
       <c r="D25" s="10">
-        <f>+'SIM①_コンサル'!G68+D29*D30</f>
+        <f>+SIM①_コンサル!G68+D29*D30</f>
+        <v>5000</v>
       </c>
       <c r="E25" s="10">
-        <f>+'SIM①_コンサル'!J68+E29*E30</f>
+        <f>+SIM①_コンサル!J68+E29*E30</f>
+        <v>5000</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -5768,12 +6073,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -5788,12 +6096,15 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -5832,395 +6143,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CA14B7-1E76-4B86-9C33-BD8F21953694}">
-  <dimension ref="A2:J42"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="14.25" customWidth="1"/>
-    <col min="5" max="5" width="14.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="59" t="s">
-        <v>80</v>
-      </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="54" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="60">
-        <v>8.5000000000000006E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>89</v>
-      </c>
-      <c r="B6" s="60">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="E7">
-        <f>+E4*B5*B6</f>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="54" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="60">
-        <v>5.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" t="s">
-        <v>89</v>
-      </c>
-      <c r="B11" s="60">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="E12">
-        <f>+E9*B10*B11</f>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="60">
-        <v>0.9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="60">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E17">
-        <f>+E14*B15*B16</f>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" s="60">
-        <v>0.7</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="60">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="E22">
-        <f>+E19*B20*B21</f>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="59" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="59"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="59"/>
-      <c r="G23" s="59"/>
-      <c r="I23" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="J23" s="68"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="I24" s="66">
-        <v>1</v>
-      </c>
-      <c r="J24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="61">
-        <v>0.8</v>
-      </c>
-      <c r="I25" s="66">
-        <v>2</v>
-      </c>
-      <c r="J25" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="61">
-        <v>0.06</v>
-      </c>
-      <c r="I26" s="66">
-        <v>3</v>
-      </c>
-      <c r="J26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
-        <v>83</v>
-      </c>
-      <c r="B27" s="61">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="I27" s="66">
-        <v>4</v>
-      </c>
-      <c r="J27" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="54" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" s="67" t="s">
-        <v>105</v>
-      </c>
-      <c r="J29" s="68"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="61">
-        <v>0.75</v>
-      </c>
-      <c r="I30" s="66">
-        <v>1</v>
-      </c>
-      <c r="J30" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="61">
-        <v>0.08</v>
-      </c>
-      <c r="I31" s="66">
-        <v>2</v>
-      </c>
-      <c r="J31" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="61">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="I32" s="66">
-        <v>3</v>
-      </c>
-      <c r="J32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="I33" s="66">
-        <v>4</v>
-      </c>
-      <c r="J33" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="54" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="62" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="61">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" t="s">
-        <v>83</v>
-      </c>
-      <c r="B37" s="61">
-        <v>4.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="54" t="s">
-        <v>96</v>
-      </c>
-      <c r="E39" s="54" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="62">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>40</v>
-      </c>
-      <c r="F40" s="62" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="61">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="E41" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" s="61">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>83</v>
-      </c>
-      <c r="B42" s="61">
-        <v>6.0000000000000001E-3</v>
-      </c>
-      <c r="F42" s="61"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF6791ED-6154-50EC-9BCF-FD3373B089C3}">
   <dimension ref="A2:Z76"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
@@ -6251,10 +6173,8 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">株式会社横浜シミズ御中_LINEOA施策提案【SIM】成果報酬（応募1件 8,000円）（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導＋通知メッセージ）</t>
-        </is>
+      <c r="A4" s="56" t="s">
+        <v>195</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -6318,7 +6238,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="147" t="s">
+      <c r="A8" s="137" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -6344,14 +6264,14 @@
         <v>5000</v>
       </c>
       <c r="N8" s="69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="148"/>
+      <c r="A9" s="138"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
@@ -6381,7 +6301,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="147" t="s">
+      <c r="A10" s="137" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -6404,14 +6324,12 @@
       </c>
       <c r="J10" s="29"/>
       <c r="K10" s="118"/>
-      <c r="N10" s="132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトからの応募は、仮に月150件（新規登録は月約300人＝マイナビの求人10件×1件30人×4週ごと。そのうち自社サイトからの応募を半分と置いた。マイナビ経由はマイナビの完了画面で終わるので、サンクスLINE誘導の母数に入れない）</t>
-        </is>
+      <c r="N10" s="132" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="148"/>
+      <c r="A11" s="138"/>
       <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
@@ -6445,10 +6363,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="149" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="149"/>
+      <c r="A13" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="139"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
@@ -6491,7 +6409,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="150" t="s">
+      <c r="A14" s="140" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -6500,24 +6418,31 @@
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>8947</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>8947</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>8947</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
@@ -6526,31 +6451,38 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="151"/>
+      <c r="A15" s="141"/>
       <c r="B15" s="20" t="s">
         <v>34</v>
       </c>
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
@@ -6568,31 +6500,38 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="152"/>
+      <c r="A16" s="142"/>
       <c r="B16" s="20" t="s">
         <v>151</v>
       </c>
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>150</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>150</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
@@ -6610,7 +6549,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="150" t="s">
+      <c r="A17" s="140" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -6655,7 +6594,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="151"/>
+      <c r="A18" s="141"/>
       <c r="B18" s="8" t="s">
         <v>172</v>
       </c>
@@ -6719,7 +6658,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="151"/>
+      <c r="A19" s="141"/>
       <c r="B19" s="8" t="s">
         <v>114</v>
       </c>
@@ -6773,13 +6712,14 @@
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="151"/>
+      <c r="A20" s="141"/>
       <c r="B20" s="8" t="s">
         <v>112</v>
       </c>
@@ -6813,8 +6753,8 @@
       <c r="Y20" s="34"/>
       <c r="Z20" s="35"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="152"/>
+    <row r="21" spans="1:26" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="142"/>
       <c r="B21" s="8" t="s">
         <v>113</v>
       </c>
@@ -6846,10 +6786,8 @@
       <c r="L21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">通知メッセージ（既存リスト）：登録済みのスタッフに配信して友だち追加。リストは仮に5,000人（マイナビの求人10件×1件30人×4週ごと＝年約3,900人の新規登録＋それ以前から続けている方）。毎月リスト×15%×15%が友だちに（FMTの式）</t>
-        </is>
+      <c r="N21" t="s">
+        <v>196</v>
       </c>
       <c r="O21" s="25" t="s">
         <v>44</v>
@@ -6862,7 +6800,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="153" t="s">
+      <c r="A22" s="143" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -6908,7 +6846,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="151"/>
+      <c r="A23" s="141"/>
       <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
@@ -6918,21 +6856,27 @@
       </c>
       <c r="E23" s="46">
         <f t="shared" ref="E23:J23" si="3">IF(E18=FALSE,0,E14*$P$18*0.125*0.125)</f>
+        <v>90.867968750000003</v>
       </c>
       <c r="F23" s="46">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="G23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="H23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="I23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="J23" s="63">
         <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
@@ -6955,7 +6899,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="151"/>
+      <c r="A24" s="141"/>
       <c r="B24" s="6" t="s">
         <v>114</v>
       </c>
@@ -6965,26 +6909,32 @@
       </c>
       <c r="E24" s="46">
         <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,E16*0.8*0.4)</f>
+        <v>48</v>
       </c>
       <c r="F24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="G24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="H24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="I24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="J24" s="63">
         <f t="shared" si="4"/>
+        <v>48</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
       <c r="N24" s="69" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="O24" s="22" t="s">
         <v>43</v>
@@ -7002,7 +6952,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="152"/>
+      <c r="A25" s="142"/>
       <c r="B25" s="6" t="s">
         <v>67</v>
       </c>
@@ -7012,21 +6962,27 @@
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>112.5</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>112.5</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
+        <v>112.5</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
+        <v>112.5</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
+        <v>112.5</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
+        <v>112.5</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
@@ -7044,36 +7000,42 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="137" t="s">
+      <c r="A26" s="144" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="138"/>
+      <c r="B26" s="145"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>296.10296875</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>296.10296875</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>296.10296875</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
+        <v>296.10296875</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
+        <v>296.10296875</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
+        <v>296.10296875</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
       <c r="N26" s="72" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O26" s="17" t="s">
         <v>40</v>
@@ -7088,10 +7050,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="137" t="s">
+      <c r="A27" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="138"/>
+      <c r="B27" s="145"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0</v>
@@ -7101,18 +7063,23 @@
       </c>
       <c r="F27" s="47">
         <f>+E$27*1.025</f>
+        <v>0.32799999999999996</v>
       </c>
       <c r="G27" s="47">
         <f>+F$27*1.025</f>
+        <v>0.33619999999999994</v>
       </c>
       <c r="H27" s="47">
         <f>+G$27*1.025</f>
+        <v>0.34460499999999994</v>
       </c>
       <c r="I27" s="47">
         <f>+H$27*1.025</f>
+        <v>0.35322012499999988</v>
       </c>
       <c r="J27" s="47">
         <f>+I$27*1.025</f>
+        <v>0.36205062812499983</v>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
@@ -7135,31 +7102,37 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="154" t="s">
+      <c r="A28" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="155"/>
+      <c r="B28" s="147"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>0</v>
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>296.10296875</v>
       </c>
       <c r="F28" s="49">
         <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
+        <v>592.2059375</v>
       </c>
       <c r="G28" s="49">
         <f t="shared" si="7"/>
+        <v>888.30890625000006</v>
       </c>
       <c r="H28" s="49">
         <f t="shared" si="7"/>
+        <v>1184.411875</v>
       </c>
       <c r="I28" s="49">
         <f t="shared" si="7"/>
+        <v>1480.51484375</v>
       </c>
       <c r="J28" s="49">
         <f t="shared" si="7"/>
+        <v>1776.6178124999999</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
@@ -7179,31 +7152,38 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="143" t="s">
+      <c r="A29" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="144"/>
+      <c r="B29" s="149"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>201.35001874999998</v>
       </c>
       <c r="F29" s="50">
         <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
+        <v>397.96239000000003</v>
       </c>
       <c r="G29" s="50">
         <f t="shared" si="8"/>
+        <v>589.65945196875009</v>
       </c>
       <c r="H29" s="50">
         <f t="shared" si="8"/>
+        <v>776.25762081562505</v>
       </c>
       <c r="I29" s="50">
         <f t="shared" si="8"/>
+        <v>957.56720557626966</v>
       </c>
       <c r="J29" s="50">
         <f t="shared" si="8"/>
+        <v>1133.3922175463119</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
@@ -7217,10 +7197,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="141" t="s">
+      <c r="A30" s="135" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="142"/>
+      <c r="B30" s="136"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -7259,31 +7239,38 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="137" t="s">
+      <c r="A31" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="138"/>
+      <c r="B31" s="145"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>0</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>73.581221987988044</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>145.43112110567051</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>215.48477274541091</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>226.94007051678793</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>279.94619741022456</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>331.34890128728421</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -7294,10 +7281,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="141" t="s">
+      <c r="A32" s="135" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="142"/>
+      <c r="B32" s="136"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -7323,7 +7310,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
       <c r="N32" s="69" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O32" s="17" t="s">
         <v>125</v>
@@ -7333,6 +7320,7 @@
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
@@ -7340,31 +7328,37 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="137" t="s">
+      <c r="A33" s="144" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="138"/>
+      <c r="B33" s="145"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="63">
         <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>20.517840746650506</v>
       </c>
       <c r="F33" s="63">
         <f t="shared" ref="F33:G33" si="9">+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>40.552908769850418</v>
       </c>
       <c r="G33" s="63">
         <f t="shared" si="9"/>
+        <v>60.08710009247033</v>
       </c>
       <c r="H33" s="63">
         <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>63.281365817181239</v>
       </c>
       <c r="I33" s="63">
         <f t="shared" ref="I33:J33" si="10">+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>78.061920431697217</v>
       </c>
       <c r="J33" s="63">
         <f t="shared" si="10"/>
+        <v>92.395366705108074</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
@@ -7376,34 +7370,42 @@
       </c>
       <c r="Q33" s="73">
         <f t="shared" ref="Q33:Q35" si="11">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="143" t="s">
+      <c r="A34" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="144"/>
+      <c r="B34" s="149"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>0</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E29*E32*$P$28</f>
+        <v>805.40007500000002</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F29*F32*$P$28</f>
+        <v>1591.8495600000003</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G29*G32*$P$28</f>
+        <v>2358.6378078750004</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
+        <v>2484.0243866100004</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
+        <v>3064.2150578440633</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
+        <v>3626.8550961481988</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
@@ -7415,34 +7417,42 @@
       </c>
       <c r="Q34" s="73">
         <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="143" t="s">
+      <c r="A35" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="144"/>
+      <c r="B35" s="149"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>0</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>192.90307860600905</v>
       </c>
       <c r="F35" s="50">
         <f t="shared" ref="F35:J35" si="12">+F31+F33+1.05*(F31+F33)</f>
+        <v>381.26726124481797</v>
       </c>
       <c r="G35" s="50">
         <f t="shared" si="12"/>
+        <v>564.92233931765657</v>
       </c>
       <c r="H35" s="50">
         <f t="shared" si="12"/>
+        <v>594.95394448463685</v>
       </c>
       <c r="I35" s="50">
         <f t="shared" si="12"/>
+        <v>733.91664157593959</v>
       </c>
       <c r="J35" s="50">
         <f t="shared" si="12"/>
+        <v>868.67574938440418</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
@@ -7454,14 +7464,16 @@
       </c>
       <c r="Q35" s="73">
         <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="145" t="s">
+      <c r="A36" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>新規応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
@@ -7471,7 +7483,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="111">
         <v>4</v>
@@ -7480,30 +7492,33 @@
         <v>5</v>
       </c>
       <c r="I36" s="111">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J36" s="111">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>29</v>
       </c>
       <c r="L36" s="7"/>
       <c r="N36" s="69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O36" s="17" t="s">
         <v>126</v>
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="146"/>
-      <c r="B37" s="6">
+      <c r="A37" s="151"/>
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -7529,6 +7544,7 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -7536,11 +7552,12 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="145" t="s">
+      <c r="A38" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>再応募</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -7550,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="111">
         <v>1</v>
@@ -7562,23 +7579,25 @@
         <v>3</v>
       </c>
       <c r="J38" s="111">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>12</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O38" s="21" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="146"/>
-      <c r="B39" s="6">
+      <c r="A39" s="151"/>
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -7604,6 +7623,7 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
@@ -7614,34 +7634,42 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="139" t="s">
+      <c r="A40" s="152" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="140"/>
+      <c r="B40" s="153"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
         <f t="shared" si="13"/>
+        <v>2</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="13"/>
+        <v>4</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="13"/>
+        <v>5</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="13"/>
+        <v>7</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="13"/>
+        <v>10</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="13"/>
+        <v>13</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>41</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -7652,24 +7680,31 @@
       </c>
       <c r="D41" s="18">
         <f t="shared" ref="D41" si="14">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
+        <v>1.0367900888118323E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="15">+IFERROR(F40/F35,0)</f>
+        <v>1.0491328279643539E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="15"/>
+        <v>8.8507740834594499E-3</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="15"/>
+        <v>1.1765616590816227E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="15"/>
+        <v>1.3625525616270255E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="15"/>
+        <v>1.49653078369145E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>116</v>
@@ -7697,245 +7732,297 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="137" t="s">
+      <c r="A44" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="138"/>
+      <c r="B44" s="145"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F44" s="31">
         <f t="shared" ref="F44:J44" si="16">+F75*F76</f>
+        <v>0</v>
       </c>
       <c r="G44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="H44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="I44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J44" s="31">
         <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="137" t="s">
+      <c r="A45" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="138"/>
+      <c r="B45" s="145"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E68)+SUM(E71:E72)</f>
+        <v>65000</v>
       </c>
       <c r="F45" s="27">
         <f t="shared" ref="F45:J45" si="17">SUM(F65:F68)+SUM(F71:F72)</f>
+        <v>65000</v>
       </c>
       <c r="G45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="H45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="I45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="J45" s="27">
         <f t="shared" si="17"/>
+        <v>65000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="137" t="s">
+      <c r="A46" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="138"/>
+      <c r="B46" s="145"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E46" s="28">
         <f t="shared" ref="E46:J46" si="18">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>202.63221356168859</v>
       </c>
       <c r="F46" s="28">
         <f t="shared" si="18"/>
+        <v>202.63221356168859</v>
       </c>
       <c r="G46" s="28">
         <f t="shared" si="18"/>
+        <v>202.63221356168853</v>
       </c>
       <c r="H46" s="28">
         <f t="shared" si="18"/>
+        <v>202.63221356168862</v>
       </c>
       <c r="I46" s="28">
         <f t="shared" si="18"/>
+        <v>202.63221356168862</v>
       </c>
       <c r="J46" s="28">
         <f t="shared" si="18"/>
+        <v>202.63221356168862</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="137" t="s">
+      <c r="A47" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="138"/>
+      <c r="B47" s="145"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="19">+E51/E35</f>
+        <v>419.89998596879212</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="19"/>
+        <v>254.41471078135584</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="19"/>
+        <v>185.86625575264844</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="19"/>
+        <v>203.37708678410908</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="19"/>
+        <v>197.57012143591871</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>194.54900187988849</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="137" t="s">
+      <c r="A48" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="138"/>
+      <c r="B48" s="145"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="20">+SUM(E36:E39)/E35</f>
+        <v>1.0367900888118323E-2</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="20"/>
+        <v>1.0491328279643539E-2</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="20"/>
+        <v>8.8507740834594499E-3</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="20"/>
+        <v>1.1765616590816227E-2</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="20"/>
+        <v>1.3625525616270255E-2</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="20"/>
+        <v>1.49653078369145E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="139" t="s">
+      <c r="A49" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="140"/>
+      <c r="B49" s="153"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
+        <v>40500</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
+        <v>24250</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="21"/>
+        <v>21000</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="21"/>
+        <v>17285.714285714286</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="21"/>
+        <v>14500</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="21"/>
+        <v>13000</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="139" t="s">
+      <c r="A50" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="140"/>
+      <c r="B50" s="153"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>21</v>
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>16000</v>
       </c>
       <c r="F50" s="65">
         <f t="shared" ref="F50:J50" si="22">+F36*$D$8+F38*$D$10</f>
+        <v>32000</v>
       </c>
       <c r="G50" s="65">
         <f t="shared" si="22"/>
+        <v>40000</v>
       </c>
       <c r="H50" s="65">
         <f t="shared" si="22"/>
+        <v>56000</v>
       </c>
       <c r="I50" s="65">
         <f t="shared" si="22"/>
+        <v>80000</v>
       </c>
       <c r="J50" s="65">
         <f t="shared" si="22"/>
+        <v>104000</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="135" t="s">
+      <c r="A51" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="136"/>
+      <c r="B51" s="155"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>295000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>81000</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="23">SUM(F45,F50)+F44</f>
+        <v>97000</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="23"/>
+        <v>105000</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="23"/>
+        <v>121000</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="23"/>
+        <v>145000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>169000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -7958,188 +8045,226 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="137" t="s">
+      <c r="A54" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="138"/>
+      <c r="B54" s="145"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>0</v>
       </c>
       <c r="E54" s="28">
         <f t="shared" ref="E54:J54" si="24">+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="G54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="H54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="I54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="J54" s="28">
         <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="137" t="s">
+      <c r="A55" s="144" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="138"/>
+      <c r="B55" s="145"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>215000</v>
       </c>
       <c r="F55" s="27">
         <f t="shared" ref="F55:J55" si="25">SUM(F65:F72)+F54</f>
+        <v>215000</v>
       </c>
       <c r="G55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="H55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="I55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="J55" s="27">
         <f t="shared" si="25"/>
+        <v>215000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="137" t="s">
+      <c r="A56" s="144" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="138"/>
+      <c r="B56" s="145"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E56" s="28">
         <f t="shared" ref="E56:J56" si="26">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>202.63221356168859</v>
       </c>
       <c r="F56" s="28">
         <f t="shared" si="26"/>
+        <v>202.63221356168859</v>
       </c>
       <c r="G56" s="28">
         <f t="shared" si="26"/>
+        <v>202.63221356168853</v>
       </c>
       <c r="H56" s="28">
         <f t="shared" si="26"/>
+        <v>202.63221356168862</v>
       </c>
       <c r="I56" s="28">
         <f t="shared" si="26"/>
+        <v>202.63221356168862</v>
       </c>
       <c r="J56" s="28">
         <f t="shared" si="26"/>
+        <v>202.63221356168862</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="137" t="s">
+      <c r="A57" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="138"/>
+      <c r="B57" s="145"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>1114.5493454727198</v>
       </c>
       <c r="F57" s="28">
         <f t="shared" ref="F57:J57" si="27">+F61/F35</f>
+        <v>563.9088950308402</v>
       </c>
       <c r="G57" s="28">
         <f t="shared" si="27"/>
+        <v>380.58328558875633</v>
       </c>
       <c r="H57" s="28">
         <f t="shared" si="27"/>
+        <v>361.37250957506984</v>
       </c>
       <c r="I57" s="28">
         <f t="shared" si="27"/>
+        <v>292.94880074981046</v>
       </c>
       <c r="J57" s="28">
         <f t="shared" si="27"/>
+        <v>247.50316807204749</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="137" t="s">
+      <c r="A58" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="138"/>
+      <c r="B58" s="145"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="28">+SUM(E36:E39)/E35</f>
+        <v>1.0367900888118323E-2</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="28"/>
+        <v>1.0491328279643539E-2</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="28"/>
+        <v>8.8507740834594499E-3</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="28"/>
+        <v>1.1765616590816227E-2</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="28"/>
+        <v>1.3625525616270255E-2</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="28"/>
+        <v>1.49653078369145E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="139" t="s">
+      <c r="A59" s="152" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="140"/>
+      <c r="B59" s="153"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
+        <v>107500</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
+        <v>53750</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="29"/>
+        <v>43000</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="29"/>
+        <v>30714.285714285714</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="29"/>
+        <v>21500</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="29"/>
+        <v>16538.461538461539</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="139" t="s">
+      <c r="A60" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="140"/>
+      <c r="B60" s="153"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -8152,31 +8277,38 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="135" t="s">
+      <c r="A61" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="136"/>
+      <c r="B61" s="155"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>295000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>215000</v>
       </c>
       <c r="F61" s="40">
         <f t="shared" ref="F61:J61" si="30">+SUM(F65:F72)+F54</f>
+        <v>215000</v>
       </c>
       <c r="G61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="H61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="I61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="J61" s="40">
         <f t="shared" si="30"/>
+        <v>215000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
@@ -8254,7 +8386,7 @@
         <v>30000</v>
       </c>
       <c r="N66" s="69" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8302,21 +8434,27 @@
       </c>
       <c r="E68" s="28">
         <f t="shared" ref="E68:J68" si="31">IF(E34&lt;5000,5000,15000)</f>
+        <v>5000</v>
       </c>
       <c r="F68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="G68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="H68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="I68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="J68" s="28">
         <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="N68" s="69" t="s">
         <v>176</v>
@@ -8470,24 +8608,31 @@
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>295000</v>
       </c>
       <c r="E73" s="114">
         <f t="shared" ref="E73:J73" si="32">SUM(E65:E72)+E54</f>
+        <v>215000</v>
       </c>
       <c r="F73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="G73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="H73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="I73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
       <c r="J73" s="114">
         <f t="shared" si="32"/>
+        <v>215000</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8508,24 +8653,31 @@
       </c>
       <c r="D75" s="41">
         <f t="shared" ref="D75:J75" si="33">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>0</v>
       </c>
       <c r="E75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="F75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="G75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="H75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="I75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="J75" s="41">
         <f t="shared" si="33"/>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
@@ -8534,39 +8686,47 @@
       </c>
       <c r="D76" s="5">
         <f t="shared" ref="D76:J76" si="34">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
         <f t="shared" si="34"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
@@ -8579,25 +8739,24 @@
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07296F2-79D8-5023-B49B-E468DC771929}">
   <dimension ref="A1:Y35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
@@ -8641,30 +8800,36 @@
         <v>139</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
-        <f>+'SIM②_成果報酬'!D24</f>
+      <c r="C4" s="86" t="str">
+        <f>+SIM②_成果報酬!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
-        <f>+'SIM②_成果報酬'!G51</f>
+        <f>+SIM②_成果報酬!G51</f>
+        <v>105000</v>
       </c>
       <c r="E4" s="28">
-        <f>+'SIM②_成果報酬'!J51</f>
+        <f>+SIM②_成果報酬!J51</f>
+        <v>169000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="85" t="s">
         <v>140</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
-        <f>+'SIM②_成果報酬'!D25</f>
+      <c r="C5" s="86" t="str">
+        <f>+SIM②_成果報酬!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
-        <f>+'SIM②_成果報酬'!G61</f>
+        <f>+SIM②_成果報酬!G61</f>
+        <v>215000</v>
       </c>
       <c r="E5" s="28">
-        <f>+'SIM②_成果報酬'!J61</f>
+        <f>+SIM②_成果報酬!J61</f>
+        <v>215000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -8674,13 +8839,16 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'SIM②_成果報酬'!D28</f>
+        <f>+SIM②_成果報酬!D28</f>
+        <v>0</v>
       </c>
       <c r="D6" s="87">
-        <f>+'SIM②_成果報酬'!G28</f>
+        <f>+SIM②_成果報酬!G28</f>
+        <v>888.30890625000006</v>
       </c>
       <c r="E6" s="87">
-        <f>+'SIM②_成果報酬'!J28</f>
+        <f>+SIM②_成果報酬!J28</f>
+        <v>1776.6178124999999</v>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -8690,13 +8858,16 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'SIM②_成果報酬'!D27</f>
+        <f>+SIM②_成果報酬!D27</f>
+        <v>0</v>
       </c>
       <c r="D7" s="89">
-        <f>+'SIM②_成果報酬'!G27</f>
+        <f>+SIM②_成果報酬!G27</f>
+        <v>0.33619999999999994</v>
       </c>
       <c r="E7" s="89">
-        <f>+'SIM②_成果報酬'!J27</f>
+        <f>+SIM②_成果報酬!J27</f>
+        <v>0.36205062812499983</v>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -8706,13 +8877,16 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'SIM②_成果報酬'!D29</f>
+        <f>+SIM②_成果報酬!D29</f>
+        <v>0</v>
       </c>
       <c r="D8" s="10">
-        <f>+'SIM②_成果報酬'!G29</f>
+        <f>+SIM②_成果報酬!G29</f>
+        <v>589.65945196875009</v>
       </c>
       <c r="E8" s="10">
-        <f>+'SIM②_成果報酬'!J29</f>
+        <f>+SIM②_成果報酬!J29</f>
+        <v>1133.3922175463119</v>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -8730,13 +8904,16 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'SIM②_成果報酬'!D34</f>
+        <f>+SIM②_成果報酬!D34</f>
+        <v>0</v>
       </c>
       <c r="D10" s="10">
-        <f>+'SIM②_成果報酬'!G34</f>
+        <f>+SIM②_成果報酬!G34</f>
+        <v>2358.6378078750004</v>
       </c>
       <c r="E10" s="10">
-        <f>+'SIM②_成果報酬'!J34</f>
+        <f>+SIM②_成果報酬!J34</f>
+        <v>3626.8550961481988</v>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -8746,13 +8923,16 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'SIM②_成果報酬'!D35</f>
+        <f>+SIM②_成果報酬!D35</f>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
-        <f>+'SIM②_成果報酬'!G35</f>
+        <f>+SIM②_成果報酬!G35</f>
+        <v>564.92233931765657</v>
       </c>
       <c r="E11" s="10">
-        <f>+'SIM②_成果報酬'!J35</f>
+        <f>+SIM②_成果報酬!J35</f>
+        <v>868.67574938440418</v>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -8763,28 +8943,34 @@
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>185.86625575264844</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>194.54900187988849</v>
       </c>
       <c r="F12" s="28"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="85" t="s">
         <v>147</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>380.58328558875633</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>247.50316807204749</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -8805,13 +8991,16 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'SIM②_成果報酬'!$H$10</f>
+        <f>+SIM②_成果報酬!$H$10</f>
+        <v>150</v>
       </c>
       <c r="D15" s="87">
-        <f>+'SIM②_成果報酬'!$H$10</f>
+        <f>+SIM②_成果報酬!$H$10</f>
+        <v>150</v>
       </c>
       <c r="E15" s="87">
-        <f>+'SIM②_成果報酬'!$H$10</f>
+        <f>+SIM②_成果報酬!$H$10</f>
+        <v>150</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -8825,12 +9014,15 @@
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>SUM(C17:C20)</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
+        <v>5</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
+        <v>13</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -8849,13 +9041,16 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'SIM②_成果報酬'!D36</f>
+        <f>+SIM②_成果報酬!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
-        <f>+'SIM②_成果報酬'!G36</f>
+        <f>+SIM②_成果報酬!G36</f>
+        <v>4</v>
       </c>
       <c r="E17" s="87">
-        <f>+'SIM②_成果報酬'!J36</f>
+        <f>+SIM②_成果報酬!J36</f>
+        <v>8</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -8886,13 +9081,16 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'SIM②_成果報酬'!D37</f>
+        <f>+SIM②_成果報酬!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
-        <f>+'SIM②_成果報酬'!G37</f>
+        <f>+SIM②_成果報酬!G37</f>
+        <v>0</v>
       </c>
       <c r="E18" s="87">
-        <f>+'SIM②_成果報酬'!J37</f>
+        <f>+SIM②_成果報酬!J37</f>
+        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -8912,6 +9110,7 @@
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
@@ -8923,13 +9122,16 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'SIM②_成果報酬'!D38</f>
+        <f>+SIM②_成果報酬!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
-        <f>+'SIM②_成果報酬'!G38</f>
+        <f>+SIM②_成果報酬!G38</f>
+        <v>1</v>
       </c>
       <c r="E19" s="87">
-        <f>+'SIM②_成果報酬'!J38</f>
+        <f>+SIM②_成果報酬!J38</f>
+        <v>5</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -8944,13 +9146,16 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'SIM②_成果報酬'!D39</f>
+        <f>+SIM②_成果報酬!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
-        <f>+'SIM②_成果報酬'!G39</f>
+        <f>+SIM②_成果報酬!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
-        <f>+'SIM②_成果報酬'!J39</f>
+        <f>+SIM②_成果報酬!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -8977,14 +9182,17 @@
         <v>141</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>21000</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>13000</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -8993,19 +9201,22 @@
       <c r="X22" s="34"/>
       <c r="Y22" s="35"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004" hidden="1">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="85" t="s">
         <v>142</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>43000</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>16538.461538461539</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -9033,13 +9244,16 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'SIM②_成果報酬'!E68+C29*C30</f>
+        <f>+SIM②_成果報酬!E68+C29*C30</f>
+        <v>5000</v>
       </c>
       <c r="D25" s="10">
-        <f>+'SIM②_成果報酬'!G68+D29*D30</f>
+        <f>+SIM②_成果報酬!G68+D29*D30</f>
+        <v>5000</v>
       </c>
       <c r="E25" s="10">
-        <f>+'SIM②_成果報酬'!J68+E29*E30</f>
+        <f>+SIM②_成果報酬!J68+E29*E30</f>
+        <v>5000</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -9075,12 +9289,15 @@
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -9095,12 +9312,15 @@
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -9131,6 +9351,399 @@
       <c r="F35" s="94" t="s">
         <v>138</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CA14B7-1E76-4B86-9C33-BD8F21953694}">
+  <dimension ref="A2:J42"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="14.25" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="60">
+        <v>8.5000000000000006E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="60">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="E7">
+        <f>+E4*B5*B6</f>
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="54" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="60">
+        <v>5.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B11" s="60">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="E12">
+        <f>+E9*B10*B11</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="60">
+        <v>0.9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="60">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17">
+        <f>+E14*B15*B16</f>
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="60">
+        <v>0.7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" s="60">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22">
+        <f>+E19*B20*B21</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="I23" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="J23" s="68"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="I24" s="66">
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="61">
+        <v>0.8</v>
+      </c>
+      <c r="I25" s="66">
+        <v>2</v>
+      </c>
+      <c r="J25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="61">
+        <v>0.06</v>
+      </c>
+      <c r="I26" s="66">
+        <v>3</v>
+      </c>
+      <c r="J26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>83</v>
+      </c>
+      <c r="B27" s="61">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I27" s="66">
+        <v>4</v>
+      </c>
+      <c r="J27" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="J29" s="68"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="61">
+        <v>0.75</v>
+      </c>
+      <c r="I30" s="66">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="61">
+        <v>0.08</v>
+      </c>
+      <c r="I31" s="66">
+        <v>2</v>
+      </c>
+      <c r="J31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="61">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="I32" s="66">
+        <v>3</v>
+      </c>
+      <c r="J32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="I33" s="66">
+        <v>4</v>
+      </c>
+      <c r="J33" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="62" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="61">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="61">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="54" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="62">
+        <v>1</v>
+      </c>
+      <c r="E40" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="62" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="61">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="E41" t="s">
+        <v>98</v>
+      </c>
+      <c r="F41" s="61">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="61">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="F42" s="61"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -9147,15 +9760,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C357D3FFD3874644B9B63D306D91E343" ma:contentTypeVersion="5" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bfcf90751a1be541a10eb2cf2bfdf12b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="79deb97c-193b-473b-ac92-dc976e68b6a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9df8bde209fb52400f7491d2ba74e6ee" ns3:_="">
     <xsd:import namespace="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
@@ -9305,6 +9909,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
   <ds:schemaRefs>
@@ -9322,14 +9935,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2519B170-E350-4E75-B7A7-F72CE5062C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9345,4 +9950,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27509D86-E120-406C-A84B-FE7DD42E9BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCC889B-B5C7-4ECC-9A56-2C7F9475ABD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="199">
   <si>
     <t>項目</t>
     <rPh sb="0" eb="2">
@@ -1587,6 +1587,13 @@
   </si>
   <si>
     <t>サンクスLINE誘導＝応募×遷移80%×追加40%（資料と同じ・定義テキストの係数）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>会員登録</t>
+    <rPh sb="0" eb="3">
+      <t>カイイントウロク</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2088,7 +2095,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2514,12 +2521,42 @@
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2541,41 +2578,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="6" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3025,7 +3035,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="147" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -3058,12 +3068,12 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>61</v>
+        <v>198</v>
       </c>
       <c r="D9" s="33">
         <v>0</v>
@@ -3088,7 +3098,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="147" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -3116,7 +3126,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
@@ -3150,10 +3160,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="149"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
@@ -3196,7 +3206,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="150" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -3238,7 +3248,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="20" t="s">
         <v>34</v>
       </c>
@@ -3287,7 +3297,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="20" t="s">
         <v>151</v>
       </c>
@@ -3336,7 +3346,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="150" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3381,7 +3391,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="151"/>
       <c r="B18" s="8" t="s">
         <v>172</v>
       </c>
@@ -3445,7 +3455,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="151"/>
       <c r="B19" s="8" t="s">
         <v>114</v>
       </c>
@@ -3506,7 +3516,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="151"/>
       <c r="B20" s="8" t="s">
         <v>112</v>
       </c>
@@ -3541,7 +3551,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="8" t="s">
         <v>113</v>
       </c>
@@ -3584,7 +3594,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="153" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -3630,7 +3640,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="151"/>
       <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
@@ -3683,7 +3693,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="151"/>
       <c r="B24" s="6" t="s">
         <v>114</v>
       </c>
@@ -3736,7 +3746,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="152"/>
       <c r="B25" s="6" t="s">
         <v>67</v>
       </c>
@@ -3784,10 +3794,10 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>20</v>
@@ -3834,10 +3844,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0</v>
@@ -3886,10 +3896,10 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>0</v>
@@ -3936,10 +3946,10 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
@@ -3981,10 +3991,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -4023,10 +4033,10 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
@@ -4065,10 +4075,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="141" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="142"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -4112,10 +4122,10 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
@@ -4158,10 +4168,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
@@ -4205,10 +4215,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
@@ -4252,7 +4262,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="145" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -4299,36 +4309,36 @@
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
-        <v>-</v>
+        <v>会員登録</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
         <v>0</v>
       </c>
       <c r="E37" s="111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" s="111">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" s="111">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H37" s="111">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I37" s="111">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J37" s="111">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -4336,7 +4346,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="145" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -4378,7 +4388,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -4418,10 +4428,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
@@ -4429,31 +4439,31 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="13"/>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -4468,27 +4478,27 @@
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
-        <v>1.6720678611998739E-2</v>
+        <v>4.1801696529996851E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="15">+IFERROR(F40/F35,0)</f>
-        <v>1.6919734309760626E-2</v>
+        <v>3.8069402196961408E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="15"/>
-        <v>1.4273954825950513E-2</v>
+        <v>3.4257491582281231E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="15"/>
-        <v>1.6264134781542722E-2</v>
+        <v>3.5238958693342565E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="15"/>
-        <v>1.5382055253557863E-2</v>
+        <v>3.5158983436703685E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="15"/>
-        <v>1.85654450634887E-2</v>
+        <v>3.7130890126977401E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>116</v>
@@ -4516,10 +4526,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>21</v>
@@ -4552,10 +4562,10 @@
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
@@ -4592,10 +4602,10 @@
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>21</v>
@@ -4628,10 +4638,10 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>21</v>
@@ -4664,82 +4674,82 @@
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="20">+SUM(E36:E39)/E35</f>
-        <v>1.6720678611998739E-2</v>
+        <v>4.1801696529996851E-2</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="20"/>
-        <v>1.6919734309760626E-2</v>
+        <v>3.8069402196961408E-2</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="20"/>
-        <v>1.4273954825950513E-2</v>
+        <v>3.4257491582281231E-2</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="20"/>
-        <v>1.6264134781542722E-2</v>
+        <v>3.5238958693342565E-2</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="20"/>
-        <v>1.5382055253557863E-2</v>
+        <v>3.5158983436703685E-2</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="20"/>
-        <v>1.85654450634887E-2</v>
+        <v>3.7130890126977401E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="140"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-        <v>32500</v>
+        <v>13000</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>16250</v>
+        <v>7222.2222222222226</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="21"/>
-        <v>13000</v>
+        <v>5416.666666666667</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="21"/>
-        <v>10833.333333333334</v>
+        <v>5000</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="21"/>
-        <v>9285.7142857142862</v>
+        <v>4062.5</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="21"/>
-        <v>6500</v>
+        <v>3250</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>21</v>
@@ -4772,10 +4782,10 @@
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
         <v>0</v>
@@ -4829,10 +4839,10 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
@@ -4866,10 +4876,10 @@
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
@@ -4903,10 +4913,10 @@
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>21</v>
@@ -4939,10 +4949,10 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>21</v>
@@ -4975,80 +4985,80 @@
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="28">+SUM(E36:E39)/E35</f>
-        <v>1.6720678611998739E-2</v>
+        <v>4.1801696529996851E-2</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="28"/>
-        <v>1.6919734309760626E-2</v>
+        <v>3.8069402196961408E-2</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="28"/>
-        <v>1.4273954825950513E-2</v>
+        <v>3.4257491582281231E-2</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="28"/>
-        <v>1.6264134781542722E-2</v>
+        <v>3.5238958693342565E-2</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="28"/>
-        <v>1.5382055253557863E-2</v>
+        <v>3.5158983436703685E-2</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="28"/>
-        <v>1.85654450634887E-2</v>
+        <v>3.7130890126977401E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="140"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
-        <v>107500</v>
+        <v>43000</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
-        <v>53750</v>
+        <v>23888.888888888891</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="29"/>
-        <v>43000</v>
+        <v>17916.666666666668</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="29"/>
-        <v>35833.333333333336</v>
+        <v>16538.461538461539</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="29"/>
-        <v>30714.285714285714</v>
+        <v>13437.5</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="29"/>
-        <v>21500</v>
+        <v>10750</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="140"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -5061,10 +5071,10 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
@@ -5499,6 +5509,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -5511,29 +5544,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5802,11 +5812,11 @@
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -5870,11 +5880,11 @@
       </c>
       <c r="D18" s="87">
         <f>+SIM①_コンサル!G37</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18" s="87">
         <f>+SIM①_コンサル!J37</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5972,11 +5982,11 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>13000</v>
+        <v>5416.666666666667</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>6500</v>
+        <v>3250</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -5996,11 +6006,11 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>43000</v>
+        <v>17916.666666666668</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>21500</v>
+        <v>10750</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -6238,7 +6248,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="147" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
@@ -6271,15 +6281,15 @@
       </c>
     </row>
     <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="138"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>61</v>
+        <v>198</v>
       </c>
       <c r="D9" s="33">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G9" s="124" t="s">
         <v>163</v>
@@ -6301,7 +6311,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="147" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -6329,7 +6339,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="138"/>
+      <c r="A11" s="148"/>
       <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
@@ -6363,10 +6373,10 @@
       <c r="V12" s="55"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="139"/>
+      <c r="A13" s="149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="149"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
         <v>28</v>
@@ -6409,7 +6419,7 @@
       <c r="V13" s="23"/>
     </row>
     <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="140" t="s">
+      <c r="A14" s="150" t="s">
         <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
@@ -6451,7 +6461,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="141"/>
+      <c r="A15" s="151"/>
       <c r="B15" s="20" t="s">
         <v>34</v>
       </c>
@@ -6500,7 +6510,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="142"/>
+      <c r="A16" s="152"/>
       <c r="B16" s="20" t="s">
         <v>151</v>
       </c>
@@ -6549,7 +6559,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="150" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -6594,7 +6604,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="141"/>
+      <c r="A18" s="151"/>
       <c r="B18" s="8" t="s">
         <v>172</v>
       </c>
@@ -6658,7 +6668,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="141"/>
+      <c r="A19" s="151"/>
       <c r="B19" s="8" t="s">
         <v>114</v>
       </c>
@@ -6719,7 +6729,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="141"/>
+      <c r="A20" s="151"/>
       <c r="B20" s="8" t="s">
         <v>112</v>
       </c>
@@ -6754,7 +6764,7 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="142"/>
+      <c r="A21" s="152"/>
       <c r="B21" s="8" t="s">
         <v>113</v>
       </c>
@@ -6800,7 +6810,7 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="143" t="s">
+      <c r="A22" s="153" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -6846,7 +6856,7 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="141"/>
+      <c r="A23" s="151"/>
       <c r="B23" s="6" t="s">
         <v>172</v>
       </c>
@@ -6899,7 +6909,7 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="141"/>
+      <c r="A24" s="151"/>
       <c r="B24" s="6" t="s">
         <v>114</v>
       </c>
@@ -6952,7 +6962,7 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="142"/>
+      <c r="A25" s="152"/>
       <c r="B25" s="6" t="s">
         <v>67</v>
       </c>
@@ -7000,10 +7010,10 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="144" t="s">
+      <c r="A26" s="137" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="145"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
         <v>20</v>
@@ -7050,10 +7060,10 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="144" t="s">
+      <c r="A27" s="137" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="145"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0</v>
@@ -7102,10 +7112,10 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="146" t="s">
+      <c r="A28" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="147"/>
+      <c r="B28" s="155"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>0</v>
@@ -7152,10 +7162,10 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="148" t="s">
+      <c r="A29" s="143" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="149"/>
+      <c r="B29" s="144"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
@@ -7197,10 +7207,10 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="135" t="s">
+      <c r="A30" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="142"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -7239,10 +7249,10 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="144" t="s">
+      <c r="A31" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="145"/>
+      <c r="B31" s="138"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
@@ -7281,10 +7291,10 @@
       <c r="Z31" s="35"/>
     </row>
     <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="135" t="s">
+      <c r="A32" s="141" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="136"/>
+      <c r="B32" s="142"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -7328,10 +7338,10 @@
       <c r="Z32" s="35"/>
     </row>
     <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="144" t="s">
+      <c r="A33" s="137" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="145"/>
+      <c r="B33" s="138"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
@@ -7374,10 +7384,10 @@
       </c>
     </row>
     <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" s="148" t="s">
+      <c r="A34" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="149"/>
+      <c r="B34" s="144"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
@@ -7421,10 +7431,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="148" t="s">
+      <c r="A35" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="149"/>
+      <c r="B35" s="144"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
@@ -7468,7 +7478,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="150" t="s">
+      <c r="A36" s="145" t="s">
         <v>5</v>
       </c>
       <c r="B36" s="6" t="str">
@@ -7515,36 +7525,36 @@
       <c r="Q36" s="73"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="151"/>
+      <c r="A37" s="146"/>
       <c r="B37" s="6" t="str">
         <f>+C9</f>
-        <v>-</v>
+        <v>会員登録</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
         <v>0</v>
       </c>
       <c r="E37" s="111">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F37" s="111">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" s="111">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H37" s="111">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I37" s="111">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J37" s="111">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
@@ -7552,7 +7562,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="150" t="s">
+      <c r="A38" s="145" t="s">
         <v>8</v>
       </c>
       <c r="B38" s="6" t="str">
@@ -7594,7 +7604,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="151"/>
+      <c r="A39" s="146"/>
       <c r="B39" s="6" t="str">
         <f>+C11</f>
         <v>-</v>
@@ -7634,10 +7644,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="B40" s="153"/>
+      <c r="B40" s="140"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
         <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
@@ -7645,31 +7655,31 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F40" s="10">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G40" s="10">
         <f t="shared" si="13"/>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H40" s="10">
         <f t="shared" si="13"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I40" s="10">
         <f t="shared" si="13"/>
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J40" s="10">
         <f t="shared" si="13"/>
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
@@ -7684,27 +7694,27 @@
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
-        <v>1.0367900888118323E-2</v>
+        <v>2.591975222029581E-2</v>
       </c>
       <c r="F41" s="18">
         <f t="shared" ref="F41:J41" si="15">+IFERROR(F40/F35,0)</f>
-        <v>1.0491328279643539E-2</v>
+        <v>2.3605488629197962E-2</v>
       </c>
       <c r="G41" s="18">
         <f t="shared" si="15"/>
-        <v>8.8507740834594499E-3</v>
+        <v>2.1241857800302678E-2</v>
       </c>
       <c r="H41" s="18">
         <f t="shared" si="15"/>
-        <v>1.1765616590816227E-2</v>
+        <v>2.3531233181632454E-2</v>
       </c>
       <c r="I41" s="18">
         <f t="shared" si="15"/>
-        <v>1.3625525616270255E-2</v>
+        <v>2.4525946109286458E-2</v>
       </c>
       <c r="J41" s="18">
         <f t="shared" si="15"/>
-        <v>1.49653078369145E-2</v>
+        <v>2.64770830960795E-2</v>
       </c>
       <c r="N41" s="69" t="s">
         <v>116</v>
@@ -7732,10 +7742,10 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="144" t="s">
+      <c r="A44" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="145"/>
+      <c r="B44" s="138"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
         <v>21</v>
@@ -7768,10 +7778,10 @@
       <c r="L44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="144" t="s">
+      <c r="A45" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="145"/>
+      <c r="B45" s="138"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
         <v>0</v>
@@ -7808,10 +7818,10 @@
       <c r="L45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="144" t="s">
+      <c r="A46" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="145"/>
+      <c r="B46" s="138"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
         <v>21</v>
@@ -7844,154 +7854,154 @@
       <c r="L46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="144" t="s">
+      <c r="A47" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="145"/>
+      <c r="B47" s="138"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E47" s="28">
         <f t="shared" ref="E47:I47" si="19">+E51/E35</f>
-        <v>419.89998596879212</v>
+        <v>458.77961429923585</v>
       </c>
       <c r="F47" s="28">
         <f t="shared" si="19"/>
-        <v>254.41471078135584</v>
+        <v>287.20011165524187</v>
       </c>
       <c r="G47" s="28">
         <f t="shared" si="19"/>
-        <v>185.86625575264844</v>
+        <v>216.84396504475652</v>
       </c>
       <c r="H47" s="28">
         <f t="shared" si="19"/>
-        <v>203.37708678410908</v>
+        <v>232.79112826114965</v>
       </c>
       <c r="I47" s="28">
         <f t="shared" si="19"/>
-        <v>197.57012143591871</v>
+        <v>224.82117266845921</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
-        <v>194.54900187988849</v>
+        <v>223.32844002780101</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="144" t="s">
+      <c r="A48" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B48" s="145"/>
+      <c r="B48" s="138"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E48" s="32">
         <f t="shared" ref="E48:J48" si="20">+SUM(E36:E39)/E35</f>
-        <v>1.0367900888118323E-2</v>
+        <v>2.591975222029581E-2</v>
       </c>
       <c r="F48" s="32">
         <f t="shared" si="20"/>
-        <v>1.0491328279643539E-2</v>
+        <v>2.3605488629197962E-2</v>
       </c>
       <c r="G48" s="32">
         <f t="shared" si="20"/>
-        <v>8.8507740834594499E-3</v>
+        <v>2.1241857800302678E-2</v>
       </c>
       <c r="H48" s="32">
         <f t="shared" si="20"/>
-        <v>1.1765616590816227E-2</v>
+        <v>2.3531233181632454E-2</v>
       </c>
       <c r="I48" s="32">
         <f t="shared" si="20"/>
-        <v>1.3625525616270255E-2</v>
+        <v>2.4525946109286458E-2</v>
       </c>
       <c r="J48" s="32">
         <f t="shared" si="20"/>
-        <v>1.49653078369145E-2</v>
+        <v>2.64770830960795E-2</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="152" t="s">
+      <c r="A49" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="153"/>
+      <c r="B49" s="140"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-        <v>40500</v>
+        <v>17700</v>
       </c>
       <c r="F49" s="28">
         <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
-        <v>24250</v>
+        <v>12166.666666666666</v>
       </c>
       <c r="G49" s="28">
         <f t="shared" si="21"/>
-        <v>21000</v>
+        <v>10208.333333333334</v>
       </c>
       <c r="H49" s="28">
         <f t="shared" si="21"/>
-        <v>17285.714285714286</v>
+        <v>9892.8571428571431</v>
       </c>
       <c r="I49" s="28">
         <f t="shared" si="21"/>
-        <v>14500</v>
+        <v>9166.6666666666661</v>
       </c>
       <c r="J49" s="28">
         <f t="shared" si="21"/>
-        <v>13000</v>
+        <v>8434.782608695652</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B50" s="153"/>
+      <c r="B50" s="140"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="E50" s="65">
-        <f>+E36*$D$8+E38*$D$10</f>
-        <v>16000</v>
-      </c>
-      <c r="F50" s="65">
-        <f t="shared" ref="F50:J50" si="22">+F36*$D$8+F38*$D$10</f>
-        <v>32000</v>
-      </c>
-      <c r="G50" s="65">
+      <c r="E50" s="156">
+        <f>+E36*$D$8+E37*$D$9+E38*$D$10</f>
+        <v>23500</v>
+      </c>
+      <c r="F50" s="156">
+        <f t="shared" ref="F50:J50" si="22">+F36*$D$8+F37*$D$9+F38*$D$10</f>
+        <v>44500</v>
+      </c>
+      <c r="G50" s="156">
         <f t="shared" si="22"/>
-        <v>40000</v>
-      </c>
-      <c r="H50" s="65">
+        <v>57500</v>
+      </c>
+      <c r="H50" s="156">
         <f t="shared" si="22"/>
-        <v>56000</v>
-      </c>
-      <c r="I50" s="65">
+        <v>73500</v>
+      </c>
+      <c r="I50" s="156">
         <f t="shared" si="22"/>
-        <v>80000</v>
-      </c>
-      <c r="J50" s="65">
+        <v>100000</v>
+      </c>
+      <c r="J50" s="156">
         <f t="shared" si="22"/>
-        <v>104000</v>
+        <v>129000</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="154" t="s">
+      <c r="A51" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="B51" s="155"/>
+      <c r="B51" s="136"/>
       <c r="C51" s="110">
         <f>+C45</f>
         <v>0</v>
@@ -8002,27 +8012,27 @@
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
-        <v>81000</v>
+        <v>88500</v>
       </c>
       <c r="F51" s="40">
         <f t="shared" ref="F51:I51" si="23">SUM(F45,F50)+F44</f>
-        <v>97000</v>
+        <v>109500</v>
       </c>
       <c r="G51" s="40">
         <f t="shared" si="23"/>
-        <v>105000</v>
+        <v>122500</v>
       </c>
       <c r="H51" s="40">
         <f t="shared" si="23"/>
-        <v>121000</v>
+        <v>138500</v>
       </c>
       <c r="I51" s="40">
         <f t="shared" si="23"/>
-        <v>145000</v>
+        <v>165000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
-        <v>169000</v>
+        <v>194000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
@@ -8045,10 +8055,10 @@
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="144" t="s">
+      <c r="A54" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="B54" s="145"/>
+      <c r="B54" s="138"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
@@ -8082,10 +8092,10 @@
       <c r="L54" s="7"/>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="144" t="s">
+      <c r="A55" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="145"/>
+      <c r="B55" s="138"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
@@ -8119,10 +8129,10 @@
       <c r="L55" s="7"/>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="144" t="s">
+      <c r="A56" s="137" t="s">
         <v>16</v>
       </c>
-      <c r="B56" s="145"/>
+      <c r="B56" s="138"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
         <v>21</v>
@@ -8155,10 +8165,10 @@
       <c r="L56" s="7"/>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="144" t="s">
+      <c r="A57" s="137" t="s">
         <v>17</v>
       </c>
-      <c r="B57" s="145"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
         <v>21</v>
@@ -8191,80 +8201,80 @@
       <c r="L57" s="7"/>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="144" t="s">
+      <c r="A58" s="137" t="s">
         <v>19</v>
       </c>
-      <c r="B58" s="145"/>
+      <c r="B58" s="138"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
         <v>21</v>
       </c>
       <c r="E58" s="32">
         <f t="shared" ref="E58:J58" si="28">+SUM(E36:E39)/E35</f>
-        <v>1.0367900888118323E-2</v>
+        <v>2.591975222029581E-2</v>
       </c>
       <c r="F58" s="32">
         <f t="shared" si="28"/>
-        <v>1.0491328279643539E-2</v>
+        <v>2.3605488629197962E-2</v>
       </c>
       <c r="G58" s="32">
         <f t="shared" si="28"/>
-        <v>8.8507740834594499E-3</v>
+        <v>2.1241857800302678E-2</v>
       </c>
       <c r="H58" s="32">
         <f t="shared" si="28"/>
-        <v>1.1765616590816227E-2</v>
+        <v>2.3531233181632454E-2</v>
       </c>
       <c r="I58" s="32">
         <f t="shared" si="28"/>
-        <v>1.3625525616270255E-2</v>
+        <v>2.4525946109286458E-2</v>
       </c>
       <c r="J58" s="32">
         <f t="shared" si="28"/>
-        <v>1.49653078369145E-2</v>
+        <v>2.64770830960795E-2</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="152" t="s">
+      <c r="A59" s="139" t="s">
         <v>18</v>
       </c>
-      <c r="B59" s="153"/>
+      <c r="B59" s="140"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
-        <v>107500</v>
+        <v>43000</v>
       </c>
       <c r="F59" s="28">
         <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
-        <v>53750</v>
+        <v>23888.888888888891</v>
       </c>
       <c r="G59" s="28">
         <f t="shared" si="29"/>
-        <v>43000</v>
+        <v>17916.666666666668</v>
       </c>
       <c r="H59" s="28">
         <f t="shared" si="29"/>
-        <v>30714.285714285714</v>
+        <v>15357.142857142857</v>
       </c>
       <c r="I59" s="28">
         <f t="shared" si="29"/>
-        <v>21500</v>
+        <v>11944.444444444445</v>
       </c>
       <c r="J59" s="28">
         <f t="shared" si="29"/>
-        <v>16538.461538461539</v>
+        <v>9347.826086956522</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A60" s="152" t="s">
+      <c r="A60" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="B60" s="153"/>
+      <c r="B60" s="140"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -8277,10 +8287,10 @@
       <c r="L60" s="7"/>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="154" t="s">
+      <c r="A61" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="B61" s="155"/>
+      <c r="B61" s="136"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
@@ -8715,6 +8725,29 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A49:B49"/>
@@ -8727,29 +8760,6 @@
     <mergeCell ref="A58:B58"/>
     <mergeCell ref="A59:B59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8806,11 +8816,11 @@
       </c>
       <c r="D4" s="28">
         <f>+SIM②_成果報酬!G51</f>
-        <v>105000</v>
+        <v>122500</v>
       </c>
       <c r="E4" s="28">
         <f>+SIM②_成果報酬!J51</f>
-        <v>169000</v>
+        <v>194000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -8947,11 +8957,11 @@
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
-        <v>185.86625575264844</v>
+        <v>216.84396504475652</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
-        <v>194.54900187988849</v>
+        <v>223.32844002780101</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -9018,11 +9028,11 @@
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
@@ -9086,11 +9096,11 @@
       </c>
       <c r="D18" s="87">
         <f>+SIM②_成果報酬!G37</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18" s="87">
         <f>+SIM②_成果報酬!J37</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -9188,11 +9198,11 @@
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-        <v>21000</v>
+        <v>10208.333333333334</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
-        <v>13000</v>
+        <v>8434.782608695652</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -9212,11 +9222,11 @@
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-        <v>43000</v>
+        <v>17916.666666666668</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-        <v>16538.461538461539</v>
+        <v>9347.826086956522</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -9752,11 +9762,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9910,26 +9921,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9953,9 +9955,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
+++ b/株式会社横浜シミズ御中_LINEOA施策提案【SIM】ver2.2.xlsx
@@ -1534,7 +1534,7 @@
     <t>再応募</t>
   </si>
   <si>
-    <t>サイトからの応募は与件に無いので、仮にUUの1.0%（月89件・資料と同じ）</t>
+    <t>サイトの応募フォームからの応募は与件に無いので、仮に月150件（サンクスLINE誘導の母数）</t>
   </si>
   <si>
     <t>サンクスLINE誘導＝応募×遷移80%×追加40%（資料と同じ・定義テキストの係数）</t>
@@ -1582,7 +1582,7 @@
     <t>株式会社横浜シミズ御中_LINEOA施策提案【SIM】成果報酬（応募1件 8,000円）（サイトのLINEボタン＋離脱防止＋サンクスLINE誘導＋通知メッセージ）</t>
   </si>
   <si>
-    <t>通知メッセージ（既存リスト）：登録済みのスタッフに配信して友だち追加。リストは仮に5,000人（マイナビの求人10件×1件30人×4週ごと＝年約3,900人の新規登録＋それ以前から続けている方）。毎月リスト×15%×15%が友だちに（FMTの式）</t>
+    <t>通知メッセージ（既存リスト）：登録済みのスタッフに配信して友だち追加。リストは仮に5,000人。毎月リスト×15%×15%が友だちに（FMTの式）</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
